--- a/Ejercicio-3/Parte-B/3.B.3/Code/datos_3B3.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.3/Code/datos_3B3.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Léeme'!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Series_brutas'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cifras_citadas'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cifras_citadas'!$A$1:$F$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -870,15 +870,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="67" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1273,8 +1273,342 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Valor del ahorro fiscal de la deuda</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>% del valor de la empresa</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GRAHAM (2000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Valor del ahorro fiscal de la deuda, neto de impuestos personales</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>% del valor de la empresa</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GRAHAM (2000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VA de las dificultades financieras, empresa BBB, ajustado por riesgo</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>% del valor previo a las dificultades</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ALMEIDA y PHILIPPON (2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VA de las dificultades financieras, empresa BBB, sin primas de riesgo</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>% del valor previo a las dificultades</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ALMEIDA y PHILIPPON (2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Costes directos de quiebra, ferrocarriles de EE. UU. (mínimo y máximo)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1-5,3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>% del valor de la empresa</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>WARNER (1977)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Costes de las dificultades financieras, estimación preferida</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>% del valor de la empresa</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ANDRADE y KAPLAN (1998), versión de documento de trabajo del NBER</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Límite a la deducción de gastos financieros netos</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>% del beneficio operativo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Art. 16 Ley 27/2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gastos financieros netos deducibles en todo caso</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>millón de euros</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Art. 16 Ley 27/2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Reserva de capitalización, reducción general</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>% del aumento de fondos propios</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Art. 25 Ley 27/2014 (desde 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Impuestos e insolvencia»</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Reserva de capitalización, reducción máxima con aumento de plantilla</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>% del aumento de fondos propios</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Art. 25 Ley 27/2014 (desde 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bloque 2, «MODIGLIANI y MILLER (1958)», nota</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Empresas con calificación AAA de S&amp;P, hace cuatro décadas y en 2020</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>65 y 5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>empresas</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>WIGGLESWORTH (2020), Financial Times</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Ejercicio-3/Parte-B/3.B.3/Code/datos_3B3.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.3/Code/datos_3B3.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Léeme'!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Series_brutas'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cifras_citadas'!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cifras_citadas'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -870,13 +870,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="39" customWidth="1" min="5" max="5"/>
     <col width="67" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1607,8 +1607,134 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Agencia»</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Efectivo de las empresas del S&amp;P 500 (octubre de 2016)</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>billones de dólares</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>FERNÁNDEZ-VILLAVERDE (2016), Nada es Gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Agencia»</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ratio de efectivo sobre activos de las empresas industriales de EE. UU., 1980-2006</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>más que se duplica</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>variación</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>BATES, KAHLE y STULZ (2009)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Información asimétrica»</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Decisiones de emisión bien clasificadas por el orden jerárquico</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>&lt; 50</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>LEARY y ROBERTS (2010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bloque 2, «Información asimétrica»</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Decisiones bien clasificadas añadiendo factores de otras teorías</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>&gt; 80</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>LEARY y ROBERTS (2010)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F24"/>
+  <autoFilter ref="A1:F28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Ejercicio-3/Parte-B/3.B.3/Code/datos_3B3.xlsx
+++ b/Ejercicio-3/Parte-B/3.B.3/Code/datos_3B3.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Léeme'!$A$1:$B$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes'!$A$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Series_brutas'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cifras_citadas'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cifras_citadas'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1733,8 +1733,284 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Recompras de las empresas del S&amp;P 500 en 2024</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>942.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>mil millones de dólares</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CAREY (2025), con datos de S&amp;P Dow Jones Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dividendos de las empresas del S&amp;P 500 en 2024</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>629.6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>mil millones de dólares</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CAREY (2025), con datos de S&amp;P Dow Jones Indices</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Empresas cotizadas de EE. UU. que pagan dividendos, 1978</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>FAMA y FRENCH (2001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Empresas cotizadas de EE. UU. que pagan dividendos, 1999</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FAMA y FRENCH (2001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Aumento de los dividendos tras la reforma de 2003 (empresas no financieras)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHETTY y SAEZ (2005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tipo máximo sobre dividendos antes y después de la reforma de 2003 en EE. UU.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>35 y 15</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CHETTY y SAEZ (2005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Escala de la base del ahorro del IRPF desde 2025 (mínimo y máximo)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19 y 30</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ley 35/2006, modificada por la Ley 7/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Impuesto especial sobre recompras en EE. UU. desde 2023</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Inflation Reduction Act de 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bloque 3, «Política de dividendos»</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Rentabilidad anormal ante aumentos y reducciones significativos del dividendo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1,34 y -3,71</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GRULLON, MICHAELY y SWAMINATHAN (2002), sin verificar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F28"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>